--- a/outputs/evaluation/decision/v1/CF_M01/run_3/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_3/CF_M01_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.8571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8444</v>
+        <v>0.9152</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.25</v>
+        <v>0.5667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.5833</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9302</v>
+        <v>0.9651</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,34 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,7 +974,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8214</v>
+        <v>0.826</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform. [...] Augmenta la seguretat del sistema al reduir les portes d’enllaç amb l’exterior, ja que l’única manera d’interactuar amb els microserveis és a través de l’Api Gateway.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform. The use of this pattern provides several advantages to the system, such as: Increases the security of the system by reducing the gateways to the outside, as the only way to interact with the microservices is through the Api Gateway.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>P_03, AU_06</t>
+          <t>AU_06, P_03</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1059,87 +1059,429 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8673</v>
+        <v>0.8376</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
       </c>
       <c r="G3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>The physical architecture does not correspond exactly to the logical architecture, as both the business layer and the data layer are divided into several different services. The goal of this is to improve the security, scalability and availability of the system.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C_01, C_02, C_03, C_04</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>P_01, P_02</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD04</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9225</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.8603</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>C_03, C_04, Low price, Previous company use</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>It is the set of cloud computing services that allows the creation of scalable and highly available applications. The use of AWS and not other cloud services has been decided due to its low price and its previous use by the company.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>C_02, C_04</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>*CF_M01_C09, *CF_M01_C10</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>46</v>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9326</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>This framework allows the creation of a secure and complex REST API in an easier way than by making direct use of NodeJS.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD05</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9857</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>The use of this language has been decided, and not JavaScript, because it is the default language for NestJS and because thanks to its static typing it allows the detection of errors at compile time.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CF_M01_AU34</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9871</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>For the data transmission to be as fast as possible, two Amazon services have been used, which allow us to perform a transmission in near real time.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>C_01, Performance</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>AU_20, AU_21</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1152,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,12 +1542,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L’objectiu d’aquests serveis és formar un data lake on s’emmagatzemi tots els històrics per poder processar-los en el mòdul analític.</t>
+          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R_24, R_25, C_03, C_04</t>
+          <t>C_03, C_04, Capacity</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1224,77 +1566,42 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.5952</v>
+        <v>0.6404</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Perquè sigui la transmissió de dades la més ràpida possible s’han fet ús de dos serveis d’Amazon, que ens permeten realitzar una transmissió en quasi temps real.</t>
+          <t>Being a serverless service, it is not necessary to manage the infrastructure when there is an increase in the set of data and users. In addition, to be able to obtain the data quickly, Athena performs the queries in parallel.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_01</t>
+          <t>C_01, Performance</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_20, AU_21</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5958</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>S’ha decidit la utilització d’aquest llenguatge, i no JavaScript, ja que és el llenguatge per defecte per NestJS i perquè gràcies al seu tipatge estàtic permet la detecció d’errors en temps de compilació.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NestJS framework, TypeScript language</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AU_13, AU_14</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5923</v>
+        <v>0.6734</v>
       </c>
     </row>
   </sheetData>
@@ -1308,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1351,26 +1658,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+          <t>*CF_M01_C08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1378,40 +1685,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6217</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M01_AD03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Gives the ability to handle partial system crashes</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>*CF_M01_C08</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M01_AU10</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>43</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.6352</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/decision/v1/CF_M01/run_3/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_3/CF_M01_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8571</v>
+        <v>0.2857</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9152</v>
+        <v>0.8943</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5667</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5833</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9651</v>
+        <v>0.9302</v>
       </c>
     </row>
     <row r="8">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8571</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="9">
@@ -726,19 +726,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -755,31 +755,31 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -792,31 +792,31 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -829,22 +829,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,28 +974,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_AD02</t>
+          <t>CF_M01_AD04</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.826</v>
+        <v>0.8673</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1009,78 +1009,78 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.8603</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform. The use of this pattern provides several advantages to the system, such as: Increases the security of the system by reducing the gateways to the outside, as the only way to interact with the microservices is through the Api Gateway.</t>
+          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_05, Security</t>
+          <t>baix preu, utilització prèvia per part de l’empresa</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_06, P_03</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M01_C07</t>
+          <t>*CF_M01_C09, *CF_M01_C10</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD05</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8376</v>
+        <v>0.9213</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1088,400 +1088,58 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The physical architecture does not correspond exactly to the logical architecture, as both the business layer and the data layer are divided into several different services. The goal of this is to improve the security, scalability and availability of the system.</t>
+          <t>S’ha decidit la utilització d’aquest llenguatge, i no JavaScript, ja que és el llenguatge per defecte per NestJS i perquè gràcies al seu tipatge estàtic permet la detecció d’errors en temps de compilació.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>C_01, C_02, C_03, C_04</t>
+          <t>detecció d’errors en temps de compilació</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>P_01, P_02</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+          <t>*CF_M01_C11</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AD_06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.9225</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.8603</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>It is the set of cloud computing services that allows the creation of scalable and highly available applications. The use of AWS and not other cloud services has been decided due to its low price and its previous use by the company.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>C_02, C_04</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>The decision was made to use AWS and not other cloud services due to its low price and its previous use by the company.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>*CF_M01_C09, *CF_M01_C10</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
         <v>46</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CF_M01_AD06</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9326</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>This framework allows the creation of a secure and complex REST API in an easier way than by making direct use of NodeJS.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>*CF_M01_C11</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AD_05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CF_M01_AD05</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.9857</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>The use of this language has been decided, and not JavaScript, because it is the default language for NestJS and because thanks to its static typing it allows the detection of errors at compile time.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>It was decided to use this language, and not JavaScript, since it is the default language for NestJS and because thanks to its static typing it allows for compile-time error detection.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>*CF_M01_C11</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>CF_M01_AU34</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CF_M01_AD07</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9871</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>For the data transmission to be as fast as possible, two Amazon services have been used, which allow us to perform a transmission in near real time.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>C_01, Performance</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>AU_20, AU_21</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>CF_M01_C01</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1494,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,71 +1195,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module.</t>
+          <t>Aquestes tecnologies són les mateixes de les quals s’utilitzen actualment a l’empresa de Waapiti.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_03, C_04, Capacity</t>
+          <t>Waapiti company standards</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_12, AU_16, AU_18, AU_19</t>
+          <t>AU_13, AU_14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6404</v>
+        <v>0.6361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Being a serverless service, it is not necessary to manage the infrastructure when there is an increase in the set of data and users. In addition, to be able to obtain the data quickly, Athena performs the queries in parallel.</t>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents. L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_01, Performance</t>
+          <t>C_02, seguretat, escalabilitat, disponibilitat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_06, AU_07, AU_08, AU_09, AU_10, P_03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.6734</v>
+        <v>0.7478</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway. Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_06, P_03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD02</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.733</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,34 +1351,164 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M01_AD01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07, CF_M01_C04, CF_M01_C02</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7478</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CF_M01_AD02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>*CF_M01_C07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CF_M01_AU10</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.733</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CF_M01_AD03</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Gives the ability to handle partial system crashes</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>*CF_M01_C08</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E4" t="n">
         <v>43</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.6352</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AD_02</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6258</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>*CF_M01_C11</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7117</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CF_M01_C01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6481</v>
       </c>
     </row>
   </sheetData>
